--- a/artfynd/A 24687-2022 artfynd.xlsx
+++ b/artfynd/A 24687-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24687-2022 artfynd.xlsx
+++ b/artfynd/A 24687-2022 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>113109901</v>
       </c>
       <c r="B4" t="n">
-        <v>87175</v>
+        <v>87392</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -977,14 +977,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>113109916</v>
       </c>
       <c r="B5" t="n">
-        <v>86180</v>
+        <v>86397</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,7 +1083,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1290,7 +1298,7 @@
         <v>113109909</v>
       </c>
       <c r="B8" t="n">
-        <v>91075</v>
+        <v>91306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,14 +1397,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>113109868</v>
       </c>
       <c r="B9" t="n">
-        <v>90105</v>
+        <v>90334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,14 +1503,18 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>113109897</v>
       </c>
       <c r="B10" t="n">
-        <v>91626</v>
+        <v>91861</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,7 +1613,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">

--- a/artfynd/A 24687-2022 artfynd.xlsx
+++ b/artfynd/A 24687-2022 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>113109901</v>
       </c>
       <c r="B4" t="n">
-        <v>87392</v>
+        <v>87409</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>113109916</v>
       </c>
       <c r="B5" t="n">
-        <v>86397</v>
+        <v>86414</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>113109909</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>91324</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>113109868</v>
       </c>
       <c r="B9" t="n">
-        <v>90334</v>
+        <v>90351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>113109897</v>
       </c>
       <c r="B10" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
